--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/141.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/141.xlsx
@@ -426,13 +426,13 @@
         <v>0.2554460956653417</v>
       </c>
       <c r="E2">
-        <v>-20.67262451050826</v>
+        <v>-21.46569267261825</v>
       </c>
       <c r="F2">
-        <v>-3.795719580965915</v>
+        <v>-3.756836843445909</v>
       </c>
       <c r="G2">
-        <v>-13.91115098224454</v>
+        <v>-14.78002505737918</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>0.3972393138448371</v>
       </c>
       <c r="E3">
-        <v>-22.83281355083471</v>
+        <v>-22.36448498221307</v>
       </c>
       <c r="F3">
-        <v>-4.286027761580734</v>
+        <v>-3.763758681463702</v>
       </c>
       <c r="G3">
-        <v>-12.30440869018503</v>
+        <v>-14.95035786673719</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>0.5121828209969402</v>
       </c>
       <c r="E4">
-        <v>-21.84744339796251</v>
+        <v>-23.87972598911821</v>
       </c>
       <c r="F4">
-        <v>-5.279338024890873</v>
+        <v>-3.695155778266056</v>
       </c>
       <c r="G4">
-        <v>-13.81907263126057</v>
+        <v>-15.11692206627792</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>0.5869853474687776</v>
       </c>
       <c r="E5">
-        <v>-23.48266652683063</v>
+        <v>-22.05685661938302</v>
       </c>
       <c r="F5">
-        <v>-4.326542382884256</v>
+        <v>-3.488204750024655</v>
       </c>
       <c r="G5">
-        <v>-13.966100629026</v>
+        <v>-14.98379106197098</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.6231721286802092</v>
       </c>
       <c r="E6">
-        <v>-26.38683692461891</v>
+        <v>-24.06799521168401</v>
       </c>
       <c r="F6">
-        <v>-3.753825727936734</v>
+        <v>-3.730560201061706</v>
       </c>
       <c r="G6">
-        <v>-13.21073781259608</v>
+        <v>-15.88099824278068</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.6242933252915362</v>
       </c>
       <c r="E7">
-        <v>-25.76302873684099</v>
+        <v>-25.64871159512508</v>
       </c>
       <c r="F7">
-        <v>-4.292576005899865</v>
+        <v>-3.20307903324626</v>
       </c>
       <c r="G7">
-        <v>-12.44148714031373</v>
+        <v>-15.79407219624727</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>0.5988642753666534</v>
       </c>
       <c r="E8">
-        <v>-26.00957997392811</v>
+        <v>-26.43463208054504</v>
       </c>
       <c r="F8">
-        <v>-3.892391713607423</v>
+        <v>-3.04258119221905</v>
       </c>
       <c r="G8">
-        <v>-13.45656160717842</v>
+        <v>-15.93355775288897</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>0.5587963273724704</v>
       </c>
       <c r="E9">
-        <v>-27.10371442497491</v>
+        <v>-27.10267196893238</v>
       </c>
       <c r="F9">
-        <v>-3.510617886842201</v>
+        <v>-2.945513099959004</v>
       </c>
       <c r="G9">
-        <v>-13.3115295236529</v>
+        <v>-15.5934403905371</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>0.5196442461051831</v>
       </c>
       <c r="E10">
-        <v>-28.77907418808618</v>
+        <v>-27.6661755282738</v>
       </c>
       <c r="F10">
-        <v>-3.7230129456548</v>
+        <v>-2.989235159846165</v>
       </c>
       <c r="G10">
-        <v>-12.40079868586123</v>
+        <v>-15.84990296932823</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.4954713688473661</v>
       </c>
       <c r="E11">
-        <v>-29.4037607800593</v>
+        <v>-28.44984289655003</v>
       </c>
       <c r="F11">
-        <v>-3.236961745122968</v>
+        <v>-2.765264494946845</v>
       </c>
       <c r="G11">
-        <v>-12.03855395772738</v>
+        <v>-15.04117653345595</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.4991222756809418</v>
       </c>
       <c r="E12">
-        <v>-29.28625189544026</v>
+        <v>-27.701888992456</v>
       </c>
       <c r="F12">
-        <v>-3.425506449674163</v>
+        <v>-2.689260957372588</v>
       </c>
       <c r="G12">
-        <v>-12.9268232544294</v>
+        <v>-15.16258398917649</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.5414694811579728</v>
       </c>
       <c r="E13">
-        <v>-30.89193530876054</v>
+        <v>-29.67368629048256</v>
       </c>
       <c r="F13">
-        <v>-3.016988781309559</v>
+        <v>-2.431161555477929</v>
       </c>
       <c r="G13">
-        <v>-12.76792159026358</v>
+        <v>-14.94370046802985</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.6281010525281191</v>
       </c>
       <c r="E14">
-        <v>-30.43941593904686</v>
+        <v>-29.74924566411516</v>
       </c>
       <c r="F14">
-        <v>-2.613398242256806</v>
+        <v>-2.540676696332441</v>
       </c>
       <c r="G14">
-        <v>-11.0520018755206</v>
+        <v>-14.63407790787447</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>0.7598186172598238</v>
       </c>
       <c r="E15">
-        <v>-31.08048487309077</v>
+        <v>-31.368655440864</v>
       </c>
       <c r="F15">
-        <v>-2.857700356690437</v>
+        <v>-1.762896862454498</v>
       </c>
       <c r="G15">
-        <v>-12.56925045374134</v>
+        <v>-14.22237392883427</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.9332045830661082</v>
       </c>
       <c r="E16">
-        <v>-32.76994686525548</v>
+        <v>-31.92103047046053</v>
       </c>
       <c r="F16">
-        <v>-2.582011401364733</v>
+        <v>-1.525022879066592</v>
       </c>
       <c r="G16">
-        <v>-10.16579767779015</v>
+        <v>-13.11059356619786</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.138834702324436</v>
       </c>
       <c r="E17">
-        <v>-31.52307183792112</v>
+        <v>-33.26620578003659</v>
       </c>
       <c r="F17">
-        <v>-1.912906743794863</v>
+        <v>-1.514909341445813</v>
       </c>
       <c r="G17">
-        <v>-8.621465235181208</v>
+        <v>-12.22338684254442</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.363149474952883</v>
       </c>
       <c r="E18">
-        <v>-34.16824382428177</v>
+        <v>-33.96738621819041</v>
       </c>
       <c r="F18">
-        <v>-3.018044949748128</v>
+        <v>-1.569381953486505</v>
       </c>
       <c r="G18">
-        <v>-9.806882954382264</v>
+        <v>-11.62471308423935</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.592574887380383</v>
       </c>
       <c r="E19">
-        <v>-35.40567652566914</v>
+        <v>-35.55420366906765</v>
       </c>
       <c r="F19">
-        <v>-2.756565808850048</v>
+        <v>-1.436853937814821</v>
       </c>
       <c r="G19">
-        <v>-8.319355092586761</v>
+        <v>-11.62095230665585</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.812314578197302</v>
       </c>
       <c r="E20">
-        <v>-38.08035707849269</v>
+        <v>-35.77716881904107</v>
       </c>
       <c r="F20">
-        <v>-1.166193172624111</v>
+        <v>-0.6863878623093865</v>
       </c>
       <c r="G20">
-        <v>-8.118015775092399</v>
+        <v>-10.26902260280589</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.008682392778673</v>
       </c>
       <c r="E21">
-        <v>-36.27382644210937</v>
+        <v>-37.25677527277919</v>
       </c>
       <c r="F21">
-        <v>-1.695032034612746</v>
+        <v>-0.7266663989031097</v>
       </c>
       <c r="G21">
-        <v>-7.721027257940008</v>
+        <v>-10.65550026223445</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.173424084447888</v>
       </c>
       <c r="E22">
-        <v>-38.28304002096131</v>
+        <v>-37.63539862999585</v>
       </c>
       <c r="F22">
-        <v>-1.890564018206555</v>
+        <v>-0.5712928386296175</v>
       </c>
       <c r="G22">
-        <v>-7.082358197871375</v>
+        <v>-9.929552705112608</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.301673075207813</v>
       </c>
       <c r="E23">
-        <v>-37.09954715165515</v>
+        <v>-37.68113379310487</v>
       </c>
       <c r="F23">
-        <v>-0.8421905168975287</v>
+        <v>0.05711578517551816</v>
       </c>
       <c r="G23">
-        <v>-6.860557169644163</v>
+        <v>-9.512616793911816</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.39270703133771</v>
       </c>
       <c r="E24">
-        <v>-38.63463843208732</v>
+        <v>-39.9153974340153</v>
       </c>
       <c r="F24">
-        <v>-1.684364319199494</v>
+        <v>0.320081845561624</v>
       </c>
       <c r="G24">
-        <v>-6.623927112139429</v>
+        <v>-8.847212403857887</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.452694989602605</v>
       </c>
       <c r="E25">
-        <v>-40.53337866630448</v>
+        <v>-40.64054397811903</v>
       </c>
       <c r="F25">
-        <v>-1.234482124576096</v>
+        <v>-0.3124744138293288</v>
       </c>
       <c r="G25">
-        <v>-7.384108057712248</v>
+        <v>-8.587290588483535</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.490446680309896</v>
       </c>
       <c r="E26">
-        <v>-36.77060035509476</v>
+        <v>-39.66554439392493</v>
       </c>
       <c r="F26">
-        <v>-0.8922595278249392</v>
+        <v>0.3212763513564609</v>
       </c>
       <c r="G26">
-        <v>-6.128971709577807</v>
+        <v>-9.440846119729818</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.515159258534279</v>
       </c>
       <c r="E27">
-        <v>-40.6842482208902</v>
+        <v>-39.36455493939762</v>
       </c>
       <c r="F27">
-        <v>-1.149793154783486</v>
+        <v>-0.08966926186574864</v>
       </c>
       <c r="G27">
-        <v>-7.951434605711825</v>
+        <v>-8.529201521331265</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.537937912821332</v>
       </c>
       <c r="E28">
-        <v>-40.76749726529073</v>
+        <v>-40.92941436200049</v>
       </c>
       <c r="F28">
-        <v>-1.675028618569943</v>
+        <v>-0.249326309979117</v>
       </c>
       <c r="G28">
-        <v>-7.819650745613904</v>
+        <v>-8.761854109451438</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.56692666821621</v>
       </c>
       <c r="E29">
-        <v>-39.9355965772936</v>
+        <v>-41.29355131811617</v>
       </c>
       <c r="F29">
-        <v>-1.271510975848637</v>
+        <v>-0.09139060932876601</v>
       </c>
       <c r="G29">
-        <v>-5.891626308055107</v>
+        <v>-8.749494844557107</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.604874939024117</v>
       </c>
       <c r="E30">
-        <v>-39.87731248616662</v>
+        <v>-40.7224037733314</v>
       </c>
       <c r="F30">
-        <v>-0.9483988150800645</v>
+        <v>-0.4272397472827836</v>
       </c>
       <c r="G30">
-        <v>-7.348429622130094</v>
+        <v>-8.272994795510066</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.654067056479928</v>
       </c>
       <c r="E31">
-        <v>-40.35586418446432</v>
+        <v>-39.56715689424541</v>
       </c>
       <c r="F31">
-        <v>-1.122157161491289</v>
+        <v>-0.5194908830955505</v>
       </c>
       <c r="G31">
-        <v>-6.02274573365459</v>
+        <v>-8.346658259520623</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.714633112626784</v>
       </c>
       <c r="E32">
-        <v>-40.24473670904589</v>
+        <v>-40.72126371682274</v>
       </c>
       <c r="F32">
-        <v>-1.837488861974385</v>
+        <v>-0.6206751329801073</v>
       </c>
       <c r="G32">
-        <v>-7.097328207356818</v>
+        <v>-8.883764133505768</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.781854499324408</v>
       </c>
       <c r="E33">
-        <v>-38.2061827687897</v>
+        <v>-39.93382107945224</v>
       </c>
       <c r="F33">
-        <v>-0.9853058963443937</v>
+        <v>-0.6420453552375289</v>
       </c>
       <c r="G33">
-        <v>-7.918288592383051</v>
+        <v>-8.352200870287557</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.854310139383371</v>
       </c>
       <c r="E34">
-        <v>-39.66660969262976</v>
+        <v>-39.59834751129487</v>
       </c>
       <c r="F34">
-        <v>-1.996482387798111</v>
+        <v>-0.5349755549560816</v>
       </c>
       <c r="G34">
-        <v>-7.137627660865243</v>
+        <v>-8.681304806581819</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.931650285084371</v>
       </c>
       <c r="E35">
-        <v>-37.58905502142776</v>
+        <v>-38.55359681950594</v>
       </c>
       <c r="F35">
-        <v>-1.839021341669564</v>
+        <v>-0.8712869219208613</v>
       </c>
       <c r="G35">
-        <v>-7.906531104116972</v>
+        <v>-8.263059606968584</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.011045565654302</v>
       </c>
       <c r="E36">
-        <v>-38.51238865674099</v>
+        <v>-38.12665084852489</v>
       </c>
       <c r="F36">
-        <v>-2.051061030866362</v>
+        <v>-1.352133490060904</v>
       </c>
       <c r="G36">
-        <v>-6.441467394155703</v>
+        <v>-8.550899419628006</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.095732007379123</v>
       </c>
       <c r="E37">
-        <v>-38.07562034097672</v>
+        <v>-37.42473944517791</v>
       </c>
       <c r="F37">
-        <v>-1.768184331586567</v>
+        <v>-1.349664126833159</v>
       </c>
       <c r="G37">
-        <v>-6.760722296479991</v>
+        <v>-8.992642625933557</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.190745349767348</v>
       </c>
       <c r="E38">
-        <v>-37.06343705579143</v>
+        <v>-36.72743187658449</v>
       </c>
       <c r="F38">
-        <v>-2.060477911501387</v>
+        <v>-1.446191295179177</v>
       </c>
       <c r="G38">
-        <v>-7.044230883862756</v>
+        <v>-7.688382507572729</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.297811945065382</v>
       </c>
       <c r="E39">
-        <v>-36.83303558094091</v>
+        <v>-36.55010428925395</v>
       </c>
       <c r="F39">
-        <v>-2.064222960529444</v>
+        <v>-1.491633045794549</v>
       </c>
       <c r="G39">
-        <v>-8.146515968421287</v>
+        <v>-8.118567947573419</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.426212427744434</v>
       </c>
       <c r="E40">
-        <v>-36.18417937566294</v>
+        <v>-35.81503987650652</v>
       </c>
       <c r="F40">
-        <v>-2.461726655906425</v>
+        <v>-1.623687235311833</v>
       </c>
       <c r="G40">
-        <v>-6.103261096844523</v>
+        <v>-7.982089968700677</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.585668868259582</v>
       </c>
       <c r="E41">
-        <v>-35.11175168360536</v>
+        <v>-37.30670102611495</v>
       </c>
       <c r="F41">
-        <v>-1.938094911411788</v>
+        <v>-1.650877566941324</v>
       </c>
       <c r="G41">
-        <v>-7.145138773053875</v>
+        <v>-8.364956968359737</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.778741204235818</v>
       </c>
       <c r="E42">
-        <v>-34.96562717295825</v>
+        <v>-35.64875152487738</v>
       </c>
       <c r="F42">
-        <v>-1.961739830557297</v>
+        <v>-1.28618550438923</v>
       </c>
       <c r="G42">
-        <v>-7.679905419885383</v>
+        <v>-8.215111977180493</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>4.016338007829559</v>
       </c>
       <c r="E43">
-        <v>-33.30639848263262</v>
+        <v>-35.23468881542594</v>
       </c>
       <c r="F43">
-        <v>-1.626011634244088</v>
+        <v>-1.656689392639365</v>
       </c>
       <c r="G43">
-        <v>-5.431054411758448</v>
+        <v>-8.227569144996991</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.306836555559034</v>
       </c>
       <c r="E44">
-        <v>-33.9947081188908</v>
+        <v>-33.90690300166693</v>
       </c>
       <c r="F44">
-        <v>-1.571473581178574</v>
+        <v>-1.441284046684993</v>
       </c>
       <c r="G44">
-        <v>-7.1535923640399</v>
+        <v>-7.631115824966658</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.647855682489268</v>
       </c>
       <c r="E45">
-        <v>-33.7847695162377</v>
+        <v>-33.78438326758449</v>
       </c>
       <c r="F45">
-        <v>-1.571337728924515</v>
+        <v>-1.2585693919147</v>
       </c>
       <c r="G45">
-        <v>-7.104690507103758</v>
+        <v>-8.192822745233864</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.042628977631559</v>
       </c>
       <c r="E46">
-        <v>-34.47861953640319</v>
+        <v>-33.19573409027691</v>
       </c>
       <c r="F46">
-        <v>-1.361319256190548</v>
+        <v>-1.244023260321541</v>
       </c>
       <c r="G46">
-        <v>-8.050256509974645</v>
+        <v>-8.673096625587359</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.488013656212835</v>
       </c>
       <c r="E47">
-        <v>-31.51757506273271</v>
+        <v>-31.73028385733947</v>
       </c>
       <c r="F47">
-        <v>-1.389760422598266</v>
+        <v>-1.655804696253175</v>
       </c>
       <c r="G47">
-        <v>-7.641186772226877</v>
+        <v>-8.14264292882037</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.968443699834136</v>
       </c>
       <c r="E48">
-        <v>-31.71593035900086</v>
+        <v>-32.65684869106342</v>
       </c>
       <c r="F48">
-        <v>-1.482789395402262</v>
+        <v>-1.063290060378745</v>
       </c>
       <c r="G48">
-        <v>-6.338904292893817</v>
+        <v>-8.562487209495663</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>6.472890489533034</v>
       </c>
       <c r="E49">
-        <v>-29.97493739732333</v>
+        <v>-30.61208154666528</v>
       </c>
       <c r="F49">
-        <v>-1.457651758196908</v>
+        <v>-1.451368591446674</v>
       </c>
       <c r="G49">
-        <v>-7.164724578976408</v>
+        <v>-8.526334923770222</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>6.986697447503462</v>
       </c>
       <c r="E50">
-        <v>-29.53008277910962</v>
+        <v>-31.92443402714122</v>
       </c>
       <c r="F50">
-        <v>-1.195162009067412</v>
+        <v>-1.461899626238464</v>
       </c>
       <c r="G50">
-        <v>-7.646088445196693</v>
+        <v>-9.652852939623466</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>7.487810504845688</v>
       </c>
       <c r="E51">
-        <v>-29.9836300686262</v>
+        <v>-29.45389004074998</v>
       </c>
       <c r="F51">
-        <v>-2.490960569918623</v>
+        <v>-1.373498742113909</v>
       </c>
       <c r="G51">
-        <v>-7.991018715202284</v>
+        <v>-9.134977810296462</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>7.959532064612214</v>
       </c>
       <c r="E52">
-        <v>-29.30168315211766</v>
+        <v>-29.9273748212314</v>
       </c>
       <c r="F52">
-        <v>-1.536916578235987</v>
+        <v>-1.015958803717587</v>
       </c>
       <c r="G52">
-        <v>-8.12273077982395</v>
+        <v>-9.130419450240378</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>8.384757516842198</v>
       </c>
       <c r="E53">
-        <v>-28.67773790836602</v>
+        <v>-29.51166951670099</v>
       </c>
       <c r="F53">
-        <v>-2.657274378480888</v>
+        <v>-1.348144072649022</v>
       </c>
       <c r="G53">
-        <v>-8.448248858422319</v>
+        <v>-8.351015592243192</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>8.743129223529095</v>
       </c>
       <c r="E54">
-        <v>-28.50789856105415</v>
+        <v>-27.62912057683367</v>
       </c>
       <c r="F54">
-        <v>-1.389458068496245</v>
+        <v>-1.037495527822971</v>
       </c>
       <c r="G54">
-        <v>-8.369713745004745</v>
+        <v>-9.258578291473539</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>9.019441419826379</v>
       </c>
       <c r="E55">
-        <v>-28.82914945702963</v>
+        <v>-27.17924472612825</v>
       </c>
       <c r="F55">
-        <v>-1.499570462248174</v>
+        <v>-1.661536998680548</v>
       </c>
       <c r="G55">
-        <v>-8.520138321483214</v>
+        <v>-9.544386944841074</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>9.202035895850882</v>
       </c>
       <c r="E56">
-        <v>-25.04654579156084</v>
+        <v>-26.37589736598931</v>
       </c>
       <c r="F56">
-        <v>-1.784645648614999</v>
+        <v>-1.547085616472754</v>
       </c>
       <c r="G56">
-        <v>-8.853565650820361</v>
+        <v>-9.567322336074005</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>9.282047377111747</v>
       </c>
       <c r="E57">
-        <v>-26.31454612829895</v>
+        <v>-26.14141536101214</v>
       </c>
       <c r="F57">
-        <v>-1.837410995438522</v>
+        <v>-1.755451496238136</v>
       </c>
       <c r="G57">
-        <v>-8.485014669126672</v>
+        <v>-9.503634527146092</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>9.254126647939016</v>
       </c>
       <c r="E58">
-        <v>-26.19400332280712</v>
+        <v>-26.19487549718534</v>
       </c>
       <c r="F58">
-        <v>-2.083465106929073</v>
+        <v>-1.867064891723939</v>
       </c>
       <c r="G58">
-        <v>-8.344470455553271</v>
+        <v>-10.15058356368544</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>9.117610593213938</v>
       </c>
       <c r="E59">
-        <v>-25.6645727091746</v>
+        <v>-25.288520189768</v>
       </c>
       <c r="F59">
-        <v>-1.929507226546965</v>
+        <v>-1.674057771973862</v>
       </c>
       <c r="G59">
-        <v>-8.97730058534388</v>
+        <v>-10.30309543046451</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>8.879698471133057</v>
       </c>
       <c r="E60">
-        <v>-25.48614659744864</v>
+        <v>-25.57749232732692</v>
       </c>
       <c r="F60">
-        <v>-2.466011800481107</v>
+        <v>-1.644167790978648</v>
       </c>
       <c r="G60">
-        <v>-9.204139045259645</v>
+        <v>-10.6302504459215</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>8.54975808301915</v>
       </c>
       <c r="E61">
-        <v>-22.79501517456744</v>
+        <v>-23.75551174481524</v>
       </c>
       <c r="F61">
-        <v>-2.291352190335637</v>
+        <v>-2.511276280472281</v>
       </c>
       <c r="G61">
-        <v>-9.256087641133616</v>
+        <v>-10.80479047018809</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>8.141334888014139</v>
       </c>
       <c r="E62">
-        <v>-23.9793033838423</v>
+        <v>-23.26623022505984</v>
       </c>
       <c r="F62">
-        <v>-2.295769873694767</v>
+        <v>-2.537079925069485</v>
       </c>
       <c r="G62">
-        <v>-8.895039939394787</v>
+        <v>-11.34830311139982</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>7.67934004813268</v>
       </c>
       <c r="E63">
-        <v>-23.74915317827693</v>
+        <v>-22.66635284093558</v>
       </c>
       <c r="F63">
-        <v>-2.626933765618551</v>
+        <v>-2.471279388795509</v>
       </c>
       <c r="G63">
-        <v>-9.497064588382555</v>
+        <v>-11.68769338138307</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>7.185939882092836</v>
       </c>
       <c r="E64">
-        <v>-22.96935037313845</v>
+        <v>-22.53004859846603</v>
       </c>
       <c r="F64">
-        <v>-2.591164861165668</v>
+        <v>-2.72468940282292</v>
       </c>
       <c r="G64">
-        <v>-9.753772577165247</v>
+        <v>-11.54819346564612</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>6.684200545561361</v>
       </c>
       <c r="E65">
-        <v>-21.32052547718152</v>
+        <v>-21.58107303643331</v>
       </c>
       <c r="F65">
-        <v>-2.822660415552018</v>
+        <v>-2.885545098568139</v>
       </c>
       <c r="G65">
-        <v>-9.890368039544589</v>
+        <v>-10.78744859924162</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>6.205916819068817</v>
       </c>
       <c r="E66">
-        <v>-23.29765757515482</v>
+        <v>-21.86197963759941</v>
       </c>
       <c r="F66">
-        <v>-3.803003415538732</v>
+        <v>-2.888498228359119</v>
       </c>
       <c r="G66">
-        <v>-10.32143982733396</v>
+        <v>-11.44567996853146</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>5.773893277278694</v>
       </c>
       <c r="E67">
-        <v>-21.90396029767078</v>
+        <v>-21.4504628466901</v>
       </c>
       <c r="F67">
-        <v>-3.02804665776953</v>
+        <v>-3.45512472616126</v>
       </c>
       <c r="G67">
-        <v>-9.12805672638542</v>
+        <v>-11.85433459788924</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>5.408750069094411</v>
       </c>
       <c r="E68">
-        <v>-19.68021051122916</v>
+        <v>-21.1525446919375</v>
       </c>
       <c r="F68">
-        <v>-3.419645750299357</v>
+        <v>-3.427066265493635</v>
       </c>
       <c r="G68">
-        <v>-10.47626872993764</v>
+        <v>-12.1629637697277</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>5.135620468759599</v>
       </c>
       <c r="E69">
-        <v>-22.36036084336751</v>
+        <v>-20.83260621074066</v>
       </c>
       <c r="F69">
-        <v>-2.854262631968818</v>
+        <v>-3.887501032461295</v>
       </c>
       <c r="G69">
-        <v>-9.061307819424428</v>
+        <v>-11.74792325910006</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>4.96621970007318</v>
       </c>
       <c r="E70">
-        <v>-21.84018358456671</v>
+        <v>-20.60839509736979</v>
       </c>
       <c r="F70">
-        <v>-3.407916067875716</v>
+        <v>-3.455274660661166</v>
       </c>
       <c r="G70">
-        <v>-9.50823857523252</v>
+        <v>-11.40092266863371</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>4.908711654858718</v>
       </c>
       <c r="E71">
-        <v>-22.06600199072029</v>
+        <v>-19.97380101978129</v>
       </c>
       <c r="F71">
-        <v>-3.586060619684763</v>
+        <v>-3.908808298796104</v>
       </c>
       <c r="G71">
-        <v>-10.09233132499623</v>
+        <v>-11.3636151284267</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>4.970493628347412</v>
       </c>
       <c r="E72">
-        <v>-23.12953558072576</v>
+        <v>-21.72243173708517</v>
       </c>
       <c r="F72">
-        <v>-3.577275783378075</v>
+        <v>-3.811564592646664</v>
       </c>
       <c r="G72">
-        <v>-9.029670816469316</v>
+        <v>-10.54205035602763</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>5.142799199533652</v>
       </c>
       <c r="E73">
-        <v>-19.45528089229909</v>
+        <v>-20.59446937979764</v>
       </c>
       <c r="F73">
-        <v>-3.829525254674163</v>
+        <v>-4.076560981537032</v>
       </c>
       <c r="G73">
-        <v>-9.037309855142913</v>
+        <v>-10.76818522027609</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>5.414696372472778</v>
       </c>
       <c r="E74">
-        <v>-22.45019895753488</v>
+        <v>-21.80945812718563</v>
       </c>
       <c r="F74">
-        <v>-4.081351430227421</v>
+        <v>-4.260014540030622</v>
       </c>
       <c r="G74">
-        <v>-9.281885713810702</v>
+        <v>-9.963072054917912</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>5.773139783419431</v>
       </c>
       <c r="E75">
-        <v>-22.66018532211821</v>
+        <v>-21.23312945127315</v>
       </c>
       <c r="F75">
-        <v>-3.829149175873293</v>
+        <v>-3.980926793251232</v>
       </c>
       <c r="G75">
-        <v>-8.022891990542892</v>
+        <v>-10.41108496435902</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>6.193681077019244</v>
       </c>
       <c r="E76">
-        <v>-21.03494651327498</v>
+        <v>-21.40459893403002</v>
       </c>
       <c r="F76">
-        <v>-3.870312408853205</v>
+        <v>-4.684546207026146</v>
       </c>
       <c r="G76">
-        <v>-8.676888732105951</v>
+        <v>-9.284502985263293</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>6.658699398875907</v>
       </c>
       <c r="E77">
-        <v>-21.93554131658478</v>
+        <v>-22.26313416625328</v>
       </c>
       <c r="F77">
-        <v>-3.952551067868335</v>
+        <v>-4.579268993804357</v>
       </c>
       <c r="G77">
-        <v>-8.065766943590448</v>
+        <v>-9.221495275301365</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>7.152572993748133</v>
       </c>
       <c r="E78">
-        <v>-23.45527194493206</v>
+        <v>-22.20978616678585</v>
       </c>
       <c r="F78">
-        <v>-4.524221494786121</v>
+        <v>-4.554299515181771</v>
       </c>
       <c r="G78">
-        <v>-7.346583825704177</v>
+        <v>-8.943931353352566</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>7.653842510767715</v>
       </c>
       <c r="E79">
-        <v>-23.67368932850479</v>
+        <v>-22.37896307689142</v>
       </c>
       <c r="F79">
-        <v>-4.470390039115196</v>
+        <v>-4.292528788957905</v>
       </c>
       <c r="G79">
-        <v>-8.095115628911449</v>
+        <v>-8.93646201307739</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>8.153468363766443</v>
       </c>
       <c r="E80">
-        <v>-23.99545522268456</v>
+        <v>-23.2549999416375</v>
       </c>
       <c r="F80">
-        <v>-3.43385556472698</v>
+        <v>-5.055350792643497</v>
       </c>
       <c r="G80">
-        <v>-7.903412569702887</v>
+        <v>-8.777102163235835</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>8.644534257602301</v>
       </c>
       <c r="E81">
-        <v>-24.90998820320048</v>
+        <v>-23.07912805487631</v>
       </c>
       <c r="F81">
-        <v>-3.709536236378655</v>
+        <v>-4.67536292599871</v>
       </c>
       <c r="G81">
-        <v>-7.14205287294718</v>
+        <v>-7.914778446280299</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>9.114048756942402</v>
       </c>
       <c r="E82">
-        <v>-24.98085029482471</v>
+        <v>-24.3922904115606</v>
       </c>
       <c r="F82">
-        <v>-4.473112054400795</v>
+        <v>-4.728598785507024</v>
       </c>
       <c r="G82">
-        <v>-6.716765189799417</v>
+        <v>-7.945145321991833</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>9.562150249559306</v>
       </c>
       <c r="E83">
-        <v>-26.70647222138904</v>
+        <v>-25.54457397436633</v>
       </c>
       <c r="F83">
-        <v>-4.224923240113229</v>
+        <v>-4.807618408794874</v>
       </c>
       <c r="G83">
-        <v>-5.890391425863511</v>
+        <v>-7.432788001358146</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>9.988383833265393</v>
       </c>
       <c r="E84">
-        <v>-27.17437716245555</v>
+        <v>-26.0551946939087</v>
       </c>
       <c r="F84">
-        <v>-4.522950779190227</v>
+        <v>-4.801556416141187</v>
       </c>
       <c r="G84">
-        <v>-6.479401513064579</v>
+        <v>-6.784412192899753</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>10.38284967174398</v>
       </c>
       <c r="E85">
-        <v>-29.82783065219791</v>
+        <v>-27.3305545211144</v>
       </c>
       <c r="F85">
-        <v>-4.166281454934246</v>
+        <v>-4.988265458527779</v>
       </c>
       <c r="G85">
-        <v>-6.50770981666602</v>
+        <v>-7.434328340666903</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>10.74568910739202</v>
       </c>
       <c r="E86">
-        <v>-28.24045044118615</v>
+        <v>-27.35877559206661</v>
       </c>
       <c r="F86">
-        <v>-3.633424182674631</v>
+        <v>-5.09849962228792</v>
       </c>
       <c r="G86">
-        <v>-5.726180812571667</v>
+        <v>-6.425406093431174</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>11.07527877107216</v>
       </c>
       <c r="E87">
-        <v>-30.27522288253109</v>
+        <v>-29.89794931899499</v>
       </c>
       <c r="F87">
-        <v>-5.342971552039125</v>
+        <v>-4.790194528844389</v>
       </c>
       <c r="G87">
-        <v>-6.523071437840131</v>
+        <v>-6.847592212004694</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>11.35939574754702</v>
       </c>
       <c r="E88">
-        <v>-30.13736118581473</v>
+        <v>-30.28580318838108</v>
       </c>
       <c r="F88">
-        <v>-5.370505656140777</v>
+        <v>-4.811230919038483</v>
       </c>
       <c r="G88">
-        <v>-4.753148471229972</v>
+        <v>-6.323028355035258</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>11.59330429842088</v>
       </c>
       <c r="E89">
-        <v>-32.04834716362315</v>
+        <v>-32.39578613360734</v>
       </c>
       <c r="F89">
-        <v>-5.167378371830699</v>
+        <v>-4.806412305856398</v>
       </c>
       <c r="G89">
-        <v>-5.69612331009418</v>
+        <v>-6.491664180409038</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>11.77049200608215</v>
       </c>
       <c r="E90">
-        <v>-34.43229877049738</v>
+        <v>-33.42410672139525</v>
       </c>
       <c r="F90">
-        <v>-4.681424918652398</v>
+        <v>-4.94981098695502</v>
       </c>
       <c r="G90">
-        <v>-7.028091260800494</v>
+        <v>-6.308914669775699</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>11.87641781152544</v>
       </c>
       <c r="E91">
-        <v>-35.06607051224356</v>
+        <v>-34.58504765320759</v>
       </c>
       <c r="F91">
-        <v>-4.474111065488571</v>
+        <v>-4.769073645175211</v>
       </c>
       <c r="G91">
-        <v>-5.339926371805639</v>
+        <v>-6.712324313249933</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>11.90221993207598</v>
       </c>
       <c r="E92">
-        <v>-36.94426065682548</v>
+        <v>-36.31135693624618</v>
       </c>
       <c r="F92">
-        <v>-5.325177391859588</v>
+        <v>-4.852843955518116</v>
       </c>
       <c r="G92">
-        <v>-5.767809135076969</v>
+        <v>-6.906764738162277</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>11.84027947796406</v>
       </c>
       <c r="E93">
-        <v>-38.15311095787537</v>
+        <v>-38.84544920911863</v>
       </c>
       <c r="F93">
-        <v>-5.137835476777258</v>
+        <v>-4.335937725966808</v>
       </c>
       <c r="G93">
-        <v>-7.394425720336328</v>
+        <v>-7.585166720163064</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>11.67901033329418</v>
       </c>
       <c r="E94">
-        <v>-40.77921555104373</v>
+        <v>-38.76113901922461</v>
       </c>
       <c r="F94">
-        <v>-4.832511677616402</v>
+        <v>-4.483749120220143</v>
       </c>
       <c r="G94">
-        <v>-6.181270145226988</v>
+        <v>-7.758112884856773</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>11.41509945626482</v>
       </c>
       <c r="E95">
-        <v>-42.04249783971683</v>
+        <v>-42.05414136766598</v>
       </c>
       <c r="F95">
-        <v>-4.781644948880095</v>
+        <v>-4.643067366065766</v>
       </c>
       <c r="G95">
-        <v>-7.770305062097272</v>
+        <v>-7.694115702694813</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>11.03994878572189</v>
       </c>
       <c r="E96">
-        <v>-43.12638839503094</v>
+        <v>-44.17923992550896</v>
       </c>
       <c r="F96">
-        <v>-3.904357480740862</v>
+        <v>-4.482617570347919</v>
       </c>
       <c r="G96">
-        <v>-6.955836293496843</v>
+        <v>-8.0708931405951</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>10.56489319568834</v>
       </c>
       <c r="E97">
-        <v>-45.32665177143066</v>
+        <v>-45.83745730887698</v>
       </c>
       <c r="F97">
-        <v>-4.358289563596546</v>
+        <v>-4.081966078840299</v>
       </c>
       <c r="G97">
-        <v>-8.253415516449012</v>
+        <v>-9.25801959213104</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>9.971195480271055</v>
       </c>
       <c r="E98">
-        <v>-46.5508180775437</v>
+        <v>-47.57805571547865</v>
       </c>
       <c r="F98">
-        <v>-4.642891752176372</v>
+        <v>-4.283174864245493</v>
       </c>
       <c r="G98">
-        <v>-8.238463782175707</v>
+        <v>-8.88447164528996</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>9.299318336144035</v>
       </c>
       <c r="E99">
-        <v>-49.93912001304459</v>
+        <v>-50.65085791438612</v>
       </c>
       <c r="F99">
-        <v>-4.258169765824587</v>
+        <v>-3.768877992013003</v>
       </c>
       <c r="G99">
-        <v>-9.10945778191833</v>
+        <v>-9.476260870108268</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>8.507717720377807</v>
       </c>
       <c r="E100">
-        <v>-50.3704798093611</v>
+        <v>-51.35089518112277</v>
       </c>
       <c r="F100">
-        <v>-3.889687922404686</v>
+        <v>-3.406128451020475</v>
       </c>
       <c r="G100">
-        <v>-8.557611643971759</v>
+        <v>-10.55475815532487</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>7.688998386446774</v>
       </c>
       <c r="E101">
-        <v>-53.05433169109271</v>
+        <v>-54.50155036461698</v>
       </c>
       <c r="F101">
-        <v>-3.19266065642125</v>
+        <v>-3.32509838004603</v>
       </c>
       <c r="G101">
-        <v>-8.962060363793256</v>
+        <v>-10.62732641197946</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>6.717824995223918</v>
       </c>
       <c r="E102">
-        <v>-55.91120272255677</v>
+        <v>-56.36086312542471</v>
       </c>
       <c r="F102">
-        <v>-3.46780703109812</v>
+        <v>-2.776903056956178</v>
       </c>
       <c r="G102">
-        <v>-10.66677476275118</v>
+        <v>-10.83116290667522</v>
       </c>
     </row>
   </sheetData>
